--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,124 +461,80 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>roll_no</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>photo</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>reset_token</t>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>assessment_status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>answers</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BHOOMIKA</t>
+          <t>pathima</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bhoomikaraveendhrajb123@gmail.com</t>
+          <t>pathima@gmail.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>scrypt:32768:8:1$WfN1lGOzj4Msg2IL$90f4ab5035fbc91826c863c7f376f3e639893d700870f7c499bfce70759c41fd71c9b740d9e7ebfbb2378b14929b312677916b7c74725e287f8978a882d4a8be</t>
+          <t>scrypt:32768:8:1$FMDCWOgONuycg4jX$b57b9b917d929a91c1b6ba7ca7c749e0780ef97029707fe22f3a092fd0d43662244e60d38ef585ff5ce85e00ecc592456ec3bb09cd46f0fb5bfbd587c72596a3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mca</t>
+          <t>BSc CS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>mit</t>
+          <t>Manipal InstituteOf Technology</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>04c03945-de8f-4756-9b1d-70812891faea_003-1024x639.png</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Bhoomika R</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>bhoomikaraveendhrajb1243@gmail.com</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$QhIPpy1yuvlOHOcA$0a27cda25a79af0f2f08db62ad4012357e67e562e4427d47e859c00588e3f979ae0b13cc9c1f50d8ad0d466eb813a73f5ff04248df32e987854a64c70cb0ebdb</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>mca</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>mit</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
         <v>4</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>51230429-2077-4339-958b-cef285280057_myphoto.jpg</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ram</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ram@gamil.com</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$whMDR9ileNIsPLSB$3bd89ece8eaf24c1b14fb721316229cec54eb7dc33f85d2762b31ac3f96b171b9bc10829ea4875afa70e6cbb365d0ea2dc985f173019affe55f0e0c4e939484c</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MCA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>bck</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>32a2e347-1b4b-4875-921a-1c1c63f7defd_B612_20230818_180335_890.jpg</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2c7f3629-44b6-44f3-a5ce-cc7188027b00_628542866_1562271231498226_22110.jpg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
